--- a/artfynd/A 22262-2026 artfynd.xlsx
+++ b/artfynd/A 22262-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1398,10 +1398,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>112452405</v>
+        <v>136679691</v>
       </c>
       <c r="B8" t="n">
-        <v>57144</v>
+        <v>57184</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1409,16 +1409,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1429,11 +1429,7 @@
       <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1471,22 +1467,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,16 +1508,16 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112452405</t>
+          <t>https://artportalen.se/Sighting/136679691</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>112452423</v>
+        <v>112452405</v>
       </c>
       <c r="B9" t="n">
-        <v>58129</v>
+        <v>57144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1529,16 +1525,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102623</v>
+        <v>102613</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trädlärka</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lullula arborea</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1546,16 +1542,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N9" t="inlineStr"/>
@@ -1598,14 +1590,19 @@
           <t>2023-09-30</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:02</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>sågs förbiflygande/sträckande med lockläte</t>
+          <t>2023-10-01</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,33 +1628,33 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112452423</t>
+          <t>https://artportalen.se/Sighting/112452405</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>117938252</v>
+        <v>112452423</v>
       </c>
       <c r="B10" t="n">
-        <v>57364</v>
+        <v>58129</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102954</v>
+        <v>102623</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Enkelbeckasin</t>
+          <t>Trädlärka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Gallinago gallinago</t>
+          <t>Lullula arborea</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1665,10 +1662,18 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1706,22 +1711,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>10:15</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>23:16</t>
+          <t>2023-09-30</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>sågs förbiflygande/sträckande med lockläte</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1747,16 +1747,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117938252</t>
+          <t>https://artportalen.se/Sighting/112452423</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111020693</v>
+        <v>117938252</v>
       </c>
       <c r="B11" t="n">
-        <v>58209</v>
+        <v>57364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1764,35 +1764,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102980</v>
+        <v>102954</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ladusvala</t>
+          <t>Enkelbeckasin</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hirundo rustica</t>
+          <t>Gallinago gallinago</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>besöker bebott bo</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1830,22 +1822,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>23:16</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1871,43 +1863,43 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111020693</t>
+          <t>https://artportalen.se/Sighting/117938252</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111020694</v>
+        <v>111020693</v>
       </c>
       <c r="B12" t="n">
-        <v>58212</v>
+        <v>58209</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102981</v>
+        <v>102980</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Hussvala</t>
+          <t>Ladusvala</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Delichon urbicum</t>
+          <t>Hirundo rustica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>6</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1995,48 +1987,52 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111020694</t>
+          <t>https://artportalen.se/Sighting/111020693</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111020709</v>
+        <v>111020694</v>
       </c>
       <c r="B13" t="n">
-        <v>58541</v>
+        <v>58212</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102987</v>
+        <v>102981</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Hussvala</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Delichon urbicum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>besöker bebott bo</t>
+        </is>
+      </c>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
@@ -2115,16 +2111,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111020709</t>
+          <t>https://artportalen.se/Sighting/111020694</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111020707</v>
+        <v>111020709</v>
       </c>
       <c r="B14" t="n">
-        <v>58497</v>
+        <v>58541</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2132,21 +2128,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102990</v>
+        <v>102987</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -2235,33 +2231,33 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111020707</t>
+          <t>https://artportalen.se/Sighting/111020709</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134495500</v>
+        <v>111020707</v>
       </c>
       <c r="B15" t="n">
-        <v>58485</v>
+        <v>58497</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102995</v>
+        <v>102990</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Buskskvätta</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Saxicola rubetra</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -2314,22 +2310,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2355,38 +2351,38 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134495500</t>
+          <t>https://artportalen.se/Sighting/111020707</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111020706</v>
+        <v>134495500</v>
       </c>
       <c r="B16" t="n">
-        <v>58393</v>
+        <v>58485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>102999</v>
+        <v>102995</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Buskskvätta</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Saxicola rubetra</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -2434,22 +2430,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2475,16 +2471,16 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111020706</t>
+          <t>https://artportalen.se/Sighting/134495500</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111020704</v>
+        <v>111020706</v>
       </c>
       <c r="B17" t="n">
-        <v>58388</v>
+        <v>58393</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2492,21 +2488,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>103001</v>
+        <v>102999</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2595,38 +2591,38 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111020704</t>
+          <t>https://artportalen.se/Sighting/111020706</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134495491</v>
+        <v>111020704</v>
       </c>
       <c r="B18" t="n">
-        <v>58308</v>
+        <v>58388</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103008</v>
+        <v>103001</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ärtsångare</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Curruca curruca</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1766</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2674,22 +2670,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2715,16 +2711,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134495491</t>
+          <t>https://artportalen.se/Sighting/111020704</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>112452428</v>
+        <v>134495491</v>
       </c>
       <c r="B19" t="n">
-        <v>58327</v>
+        <v>58308</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2732,16 +2728,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103015</v>
+        <v>103008</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Ärtsångare</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Curruca curruca</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2756,11 +2752,7 @@
       </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2798,22 +2790,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2839,16 +2831,16 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112452428</t>
+          <t>https://artportalen.se/Sighting/134495491</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134495499</v>
+        <v>112452428</v>
       </c>
       <c r="B20" t="n">
-        <v>58461</v>
+        <v>58327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,21 +2848,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103018</v>
+        <v>103015</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -2880,7 +2872,11 @@
       </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2918,22 +2914,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>22:10</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2959,52 +2955,48 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134495499</t>
+          <t>https://artportalen.se/Sighting/112452428</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>112452418</v>
+        <v>134495499</v>
       </c>
       <c r="B21" t="n">
-        <v>58114</v>
+        <v>58461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3042,22 +3034,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>22:10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3083,44 +3075,52 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112452418</t>
+          <t>https://artportalen.se/Sighting/134495499</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>117938286</v>
+        <v>112452418</v>
       </c>
       <c r="B22" t="n">
-        <v>58602</v>
+        <v>58114</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103042</v>
+        <v>103021</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Grönfink</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Chloris chloris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3158,22 +3158,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-06-20</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>23:16</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3199,16 +3199,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117938286</t>
+          <t>https://artportalen.se/Sighting/112452418</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111020714</v>
+        <v>136679718</v>
       </c>
       <c r="B23" t="n">
-        <v>58636</v>
+        <v>58627</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3216,28 +3216,24 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>103044</v>
+        <v>103041</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Grönsiska</t>
+          <t>Bergfink</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Spinus spinus</t>
+          <t>Fringilla montifringilla</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
@@ -3278,22 +3274,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:54</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3319,38 +3315,38 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111020714</t>
+          <t>https://artportalen.se/Sighting/136679718</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>117938285</v>
+        <v>117938286</v>
       </c>
       <c r="B24" t="n">
-        <v>58586</v>
+        <v>58602</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103051</v>
+        <v>103042</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rosenfink</t>
+          <t>Grönfink</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carpodacus erythrinus</t>
+          <t>Chloris chloris</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Pallas, 1770)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3435,38 +3431,38 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/117938285</t>
+          <t>https://artportalen.se/Sighting/117938286</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112452448</v>
+        <v>111020714</v>
       </c>
       <c r="B25" t="n">
-        <v>58676</v>
+        <v>58636</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103055</v>
+        <v>103044</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Gulsparv</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Emberiza citrinella</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3476,11 +3472,7 @@
       </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3518,22 +3510,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-09-30</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>11:02</t>
+          <t>08:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-10-01</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>17:46</t>
+          <t>20:35</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3559,45 +3551,41 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112452448</t>
+          <t>https://artportalen.se/Sighting/111020714</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119863735</v>
+        <v>117938285</v>
       </c>
       <c r="B26" t="n">
-        <v>58649</v>
+        <v>58586</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>103057</v>
+        <v>103051</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Sävsparv</t>
+          <t>Rosenfink</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Emberiza schoeniclus</t>
+          <t>Carpodacus erythrinus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Pallas, 1770)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -3638,22 +3626,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2024-06-20</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>23:16</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3679,33 +3667,33 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119863735</t>
+          <t>https://artportalen.se/Sighting/117938285</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119863705</v>
+        <v>112452448</v>
       </c>
       <c r="B27" t="n">
-        <v>58085</v>
+        <v>58676</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>205976</v>
+        <v>103055</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Gulsparv</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Emberiza citrinella</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -3713,10 +3701,18 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
@@ -3754,22 +3750,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-09-13</t>
+          <t>2023-09-30</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:02</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-09-19</t>
+          <t>2023-10-01</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3795,16 +3791,16 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119863705</t>
+          <t>https://artportalen.se/Sighting/112452448</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>98274676</v>
+        <v>119863735</v>
       </c>
       <c r="B28" t="n">
-        <v>56905</v>
+        <v>58649</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3812,16 +3808,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>208260</v>
+        <v>103057</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Sävsparv</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Emberiza schoeniclus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3834,7 +3830,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
@@ -3875,22 +3870,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2020-06-20</t>
+          <t>2024-09-19</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3899,7 +3894,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3916,6 +3910,244 @@
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119863735</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>119863705</v>
+      </c>
+      <c r="B29" t="n">
+        <v>58085</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>205976</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Gråkråka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Corvus corone cornix</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Finnsjön 903,Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>559046</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6914018</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-09-13</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-09-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Michael Wikinger</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Michael Wikinger</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119863705</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>98274676</v>
+      </c>
+      <c r="B30" t="n">
+        <v>56905</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Finnsjön 903,Ånge, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>559046</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6914018</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2020-06-20</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2020-06-20</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Michael Wikinger</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Michael Wikinger</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/98274676</t>
         </is>
@@ -3950,6 +4182,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22262-2026 artfynd.xlsx
+++ b/artfynd/A 22262-2026 artfynd.xlsx
@@ -1401,7 +1401,7 @@
         <v>136679691</v>
       </c>
       <c r="B8" t="n">
-        <v>57184</v>
+        <v>57186</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>136679718</v>
       </c>
       <c r="B23" t="n">
-        <v>58627</v>
+        <v>58629</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 22262-2026 artfynd.xlsx
+++ b/artfynd/A 22262-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>112452406</v>
       </c>
       <c r="B3" t="n">
-        <v>57966</v>
+        <v>58021</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>119863701</v>
       </c>
       <c r="B5" t="n">
-        <v>57945</v>
+        <v>58000</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22262-2026 artfynd.xlsx
+++ b/artfynd/A 22262-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>112452406</v>
       </c>
       <c r="B3" t="n">
-        <v>58021</v>
+        <v>58034</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>119863701</v>
       </c>
       <c r="B5" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136679691</v>
       </c>
       <c r="B8" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>136679718</v>
       </c>
       <c r="B23" t="n">
-        <v>58629</v>
+        <v>58642</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 22262-2026 artfynd.xlsx
+++ b/artfynd/A 22262-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>112452406</v>
       </c>
       <c r="B3" t="n">
-        <v>58034</v>
+        <v>58036</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1051,7 +1051,7 @@
         <v>119863701</v>
       </c>
       <c r="B5" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136679691</v>
       </c>
       <c r="B8" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -3208,7 +3208,7 @@
         <v>136679718</v>
       </c>
       <c r="B23" t="n">
-        <v>58642</v>
+        <v>58644</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>

--- a/artfynd/A 22262-2026 artfynd.xlsx
+++ b/artfynd/A 22262-2026 artfynd.xlsx
@@ -835,11 +835,7 @@
       </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>

--- a/artfynd/A 22262-2026 artfynd.xlsx
+++ b/artfynd/A 22262-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>112452406</v>
       </c>
       <c r="B3" t="n">
-        <v>58036</v>
+        <v>58046</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>119863701</v>
       </c>
       <c r="B5" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22262-2026 artfynd.xlsx
+++ b/artfynd/A 22262-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>112452406</v>
       </c>
       <c r="B3" t="n">
-        <v>58046</v>
+        <v>58047</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>119863701</v>
       </c>
       <c r="B5" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22262-2026 artfynd.xlsx
+++ b/artfynd/A 22262-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>112452406</v>
       </c>
       <c r="B3" t="n">
-        <v>58047</v>
+        <v>58048</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>119863701</v>
       </c>
       <c r="B5" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 22262-2026 artfynd.xlsx
+++ b/artfynd/A 22262-2026 artfynd.xlsx
@@ -803,7 +803,7 @@
         <v>112452406</v>
       </c>
       <c r="B3" t="n">
-        <v>58048</v>
+        <v>58051</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>119863701</v>
       </c>
       <c r="B5" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
